--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487649_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487649_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.2384</v>
+        <v>8.524100000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8075</v>
+        <v>7.5292</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4309</v>
+        <v>0.9949</v>
       </c>
       <c r="G2" t="n">
         <v>8.3306</v>
@@ -610,13 +610,13 @@
         <v>1.1642</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5116000000000001</v>
+        <v>-0.226</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9085</v>
+        <v>-0.1868</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3969</v>
+        <v>-0.0392</v>
       </c>
       <c r="V2" t="n">
         <v>2.1657</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3281</v>
+        <v>3.8067</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2073</v>
+        <v>0.7489</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1207</v>
+        <v>3.0578</v>
       </c>
       <c r="G3" t="n">
         <v>3.7622</v>
@@ -688,13 +688,13 @@
         <v>2.1344</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6718</v>
+        <v>1.1505</v>
       </c>
       <c r="T3" t="n">
-        <v>1.227</v>
+        <v>0.7685</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4449</v>
+        <v>0.382</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3299</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.308</v>
+        <v>3.6956</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3641</v>
+        <v>3.4247</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0562</v>
+        <v>0.2709</v>
       </c>
       <c r="G4" t="n">
         <v>5.1155</v>
@@ -766,13 +766,13 @@
         <v>0.9702</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8374</v>
+        <v>-0.4497</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0595</v>
+        <v>0.0011</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7779</v>
+        <v>-0.4508</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5084</v>
+        <v>2.1144</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1964</v>
+        <v>2.6389</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6879999999999999</v>
+        <v>-0.5245</v>
       </c>
       <c r="G5" t="n">
         <v>0.7547</v>
@@ -844,13 +844,13 @@
         <v>1.5523</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4253</v>
+        <v>1.0313</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1951</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2302</v>
+        <v>0.3937</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2239</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. COULIBALY</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.962</v>
+        <v>0.8627</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7659</v>
+        <v>0.9624</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8038</v>
+        <v>-0.0997</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5222</v>
+        <v>0.8177</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1796</v>
+        <v>0.365</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3426</v>
+        <v>0.4527</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3747</v>
+        <v>0.4136</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2935</v>
+        <v>1.0175</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.6039</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8525</v>
+        <v>0.4041</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1139</v>
+        <v>-0.6525</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2614</v>
+        <v>1.0566</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.194</v>
+        <v>0.7761</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.7761</v>
       </c>
       <c r="S6" t="n">
-        <v>1.9533</v>
+        <v>0.1629</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4569</v>
+        <v>-0.0631</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4964</v>
+        <v>0.226</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.3194</v>
+        <v>-0.894</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0955</v>
+        <v>0.6119</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2239</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>M. ESTAPE ROIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0264</v>
+        <v>0.6433</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4804</v>
+        <v>-1.7598</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.454</v>
+        <v>2.4031</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8177</v>
+        <v>-1.3683</v>
       </c>
       <c r="H7" t="n">
-        <v>0.365</v>
+        <v>-1.4195</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4527</v>
+        <v>0.0512</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4136</v>
+        <v>-1.517</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0175</v>
+        <v>-0.7785</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6039</v>
+        <v>-0.7385</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4041</v>
+        <v>0.1487</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6525</v>
+        <v>-0.641</v>
       </c>
       <c r="O7" t="n">
-        <v>1.0566</v>
+        <v>0.7897</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7761</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7761</v>
+        <v>1.9403</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6734</v>
+        <v>0.8639</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5451</v>
+        <v>0.5498</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1283</v>
+        <v>0.3141</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.894</v>
+        <v>2.1179</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6119</v>
+        <v>2.1179</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. VAL GUTIERREZ</t>
+          <t>S. COULIBALY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2052</v>
+        <v>0.4676</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7117</v>
+        <v>1.3259</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5065</v>
+        <v>-0.8584000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3168</v>
+        <v>0.5222</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0671</v>
+        <v>0.1796</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2497</v>
+        <v>0.3426</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1063</v>
+        <v>1.3747</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3192</v>
+        <v>1.2935</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2129</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2104</v>
+        <v>-0.8525</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2521</v>
+        <v>-1.1139</v>
       </c>
       <c r="O8" t="n">
-        <v>1.4626</v>
+        <v>0.2614</v>
       </c>
       <c r="P8" t="n">
+        <v>-0.194</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-0.9702</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-1.9403</v>
-      </c>
       <c r="R8" t="n">
-        <v>0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3279</v>
+        <v>1.4589</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1222</v>
+        <v>1.017</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4502</v>
+        <v>0.4419</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2239</v>
+        <v>-1.3194</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.0955</v>
       </c>
       <c r="X8" t="n">
         <v>-1.2239</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. GARCIA DELGADO</t>
+          <t>N. VIÑO LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4508</v>
+        <v>0.1424</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8884</v>
+        <v>-0.118</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4376</v>
+        <v>0.2604</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7361</v>
+        <v>1.817</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5042</v>
+        <v>0.3205</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2319</v>
+        <v>1.4965</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2529</v>
+        <v>2.3241</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6261</v>
+        <v>1.0834</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6267</v>
+        <v>1.2407</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5168</v>
+        <v>-0.5071</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1219</v>
+        <v>-0.7629</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3948</v>
+        <v>0.2558</v>
       </c>
       <c r="P9" t="n">
-        <v>0.194</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R9" t="n">
-        <v>0.194</v>
+        <v>1.5523</v>
       </c>
       <c r="S9" t="n">
-        <v>0.09130000000000001</v>
+        <v>1.2374</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3645</v>
+        <v>0.7983</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2732</v>
+        <v>0.4391</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.5537</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3299</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. ESTAPE ROIZ</t>
+          <t>D. VAL GUTIERREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4514</v>
+        <v>0.134</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9635</v>
+        <v>-0.5906</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5121</v>
+        <v>0.7246</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3683</v>
+        <v>2.3168</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4195</v>
+        <v>2.0671</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0512</v>
+        <v>0.2497</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.517</v>
+        <v>1.1063</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7785</v>
+        <v>2.3192</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7385</v>
+        <v>-1.2129</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1487</v>
+        <v>1.2104</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.641</v>
+        <v>-0.2521</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7897</v>
+        <v>1.4626</v>
       </c>
       <c r="P10" t="n">
         <v>-0.9702</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9105</v>
+        <v>-1.9403</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9403</v>
+        <v>0.9702</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2308</v>
+        <v>0.0112</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6539</v>
+        <v>0.2434</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4231</v>
+        <v>-0.2321</v>
       </c>
       <c r="V10" t="n">
-        <v>2.1179</v>
+        <v>-1.2239</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1179</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N. VIÑO LOPEZ</t>
+          <t>D. GARCIA DELGADO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5909</v>
+        <v>-0.4997</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6605</v>
+        <v>-1.1281</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0696</v>
+        <v>0.6284</v>
       </c>
       <c r="G11" t="n">
-        <v>1.817</v>
+        <v>-0.7361</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3205</v>
+        <v>-0.5042</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4965</v>
+        <v>-0.2319</v>
       </c>
       <c r="J11" t="n">
-        <v>2.3241</v>
+        <v>-1.2529</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0834</v>
+        <v>-0.6261</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2407</v>
+        <v>-0.6267</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5071</v>
+        <v>0.5168</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7629</v>
+        <v>0.1219</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2558</v>
+        <v>0.3948</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.3582</v>
+        <v>0.194</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5523</v>
+        <v>0.194</v>
       </c>
       <c r="S11" t="n">
-        <v>0.504</v>
+        <v>0.0423</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2557</v>
+        <v>0.1248</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2483</v>
+        <v>-0.0824</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.5537</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3299</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0426</v>
+        <v>-1.2339</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.256</v>
+        <v>-0.5563</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7866</v>
+        <v>-0.6776</v>
       </c>
       <c r="G12" t="n">
         <v>-1.6009</v>
@@ -1390,13 +1390,13 @@
         <v>0.3881</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1702</v>
+        <v>-0.021</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3645</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1943</v>
+        <v>-0.0852</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.3812</v>
+        <v>-1.591</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1784</v>
+        <v>-0.1404</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5597</v>
+        <v>-1.4507</v>
       </c>
       <c r="G13" t="n">
         <v>-1.4587</v>
@@ -1468,13 +1468,13 @@
         <v>1.1642</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8252</v>
+        <v>0.6155</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6202</v>
+        <v>0.3014</v>
       </c>
       <c r="U13" t="n">
-        <v>0.205</v>
+        <v>0.3141</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9418</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>15.2492</v>
+        <v>17.0662</v>
       </c>
       <c r="E14" t="n">
-        <v>10.5199</v>
+        <v>12.3368</v>
       </c>
       <c r="F14" t="n">
-        <v>4.729100000000001</v>
+        <v>4.729199999999999</v>
       </c>
       <c r="G14" t="n">
         <v>18.2727</v>
       </c>
       <c r="H14" t="n">
-        <v>5.453999999999999</v>
+        <v>5.453999999999998</v>
       </c>
       <c r="I14" t="n">
         <v>12.8186</v>
@@ -1546,19 +1546,19 @@
         <v>13.5824</v>
       </c>
       <c r="S14" t="n">
-        <v>4.06</v>
+        <v>5.877199999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4391</v>
+        <v>4.2562</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6209</v>
+        <v>1.6212</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.203</v>
+        <v>-3.202999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>6.162599999999999</v>
+        <v>6.1626</v>
       </c>
       <c r="X14" t="n">
         <v>-9.3657</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.9297</v>
+        <v>5.9015</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2454</v>
+        <v>2.2445</v>
       </c>
       <c r="F15" t="n">
-        <v>3.6843</v>
+        <v>3.657</v>
       </c>
       <c r="G15" t="n">
         <v>1.7647</v>
@@ -1624,13 +1624,13 @@
         <v>1.1642</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4859</v>
+        <v>0.4576</v>
       </c>
       <c r="T15" t="n">
-        <v>1.578</v>
+        <v>0.577</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0922</v>
+        <v>-0.1194</v>
       </c>
       <c r="V15" t="n">
         <v>3.4851</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7992</v>
+        <v>3.4599</v>
       </c>
       <c r="E16" t="n">
-        <v>4.9172</v>
+        <v>4.717</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.118</v>
+        <v>-1.257</v>
       </c>
       <c r="G16" t="n">
         <v>-1.1007</v>
@@ -1702,13 +1702,13 @@
         <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1581</v>
+        <v>-0.1811</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1189</v>
+        <v>-0.3191</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2771</v>
+        <v>0.138</v>
       </c>
       <c r="V16" t="n">
         <v>2.6074</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0046</v>
+        <v>-0.0864</v>
       </c>
       <c r="E17" t="n">
         <v>0.1884</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1931</v>
+        <v>-0.2748</v>
       </c>
       <c r="G17" t="n">
         <v>-0.3258</v>
@@ -1780,13 +1780,13 @@
         <v>0.194</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1272</v>
+        <v>0.0454</v>
       </c>
       <c r="T17" t="n">
         <v>-0.1817</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3089</v>
+        <v>0.2271</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6925</v>
+        <v>-0.7593</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8594</v>
+        <v>1.6592</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.5519</v>
+        <v>-2.4184</v>
       </c>
       <c r="G18" t="n">
         <v>-2.1021</v>
@@ -1858,13 +1858,13 @@
         <v>2.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4845</v>
+        <v>-0.5513</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3656</v>
+        <v>0.1654</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8501</v>
+        <v>-0.7167</v>
       </c>
       <c r="V18" t="n">
         <v>-1.0164</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. PINTOR HENNINGSEN</t>
+          <t>D. RODRIGUEZ GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5793</v>
+        <v>-0.9197</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.241</v>
+        <v>1.8384</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3382</v>
+        <v>-2.758</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1852</v>
+        <v>0.1848</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7736</v>
+        <v>5.122</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4115</v>
+        <v>-4.9372</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0618</v>
+        <v>4.1774</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0618</v>
+        <v>8.1357</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-3.9583</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2469</v>
+        <v>-3.9926</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8354</v>
+        <v>-3.0137</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4115</v>
+        <v>-0.9788</v>
       </c>
       <c r="P19" t="n">
-        <v>0.194</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.8806</v>
       </c>
       <c r="R19" t="n">
-        <v>0.194</v>
+        <v>2.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.906</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3028</v>
+        <v>-0.5763</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2853</v>
+        <v>-0.3297</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.7716</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.1179</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.3463</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. RODRIGUEZ GARCIA</t>
+          <t>B. PINTOR HENNINGSEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.221</v>
+        <v>-1.4975</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5371</v>
+        <v>-0.241</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.758</v>
+        <v>-1.2565</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1848</v>
+        <v>-1.1852</v>
       </c>
       <c r="H20" t="n">
-        <v>5.122</v>
+        <v>-0.7736</v>
       </c>
       <c r="I20" t="n">
-        <v>-4.9372</v>
+        <v>-0.4115</v>
       </c>
       <c r="J20" t="n">
-        <v>4.1774</v>
+        <v>0.0618</v>
       </c>
       <c r="K20" t="n">
-        <v>8.1357</v>
+        <v>0.0618</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.9583</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.9926</v>
+        <v>-1.2469</v>
       </c>
       <c r="N20" t="n">
-        <v>-3.0137</v>
+        <v>-0.8354</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9788</v>
+        <v>-0.4115</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9702</v>
+        <v>0.194</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.8806</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.9105</v>
+        <v>0.194</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.2073</v>
+        <v>-0.5064</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.8776</v>
+        <v>-0.3028</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3297</v>
+        <v>-0.2036</v>
       </c>
       <c r="V20" t="n">
-        <v>0.7716</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1179</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.3463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. OJEDA DAVILA</t>
+          <t>J. RIES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6593</v>
+        <v>-2.0267</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3765</v>
+        <v>-2.579</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2827</v>
+        <v>0.5523</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8661</v>
+        <v>-1.7632</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9177999999999999</v>
+        <v>0.2966</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0517</v>
+        <v>-2.0598</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0474</v>
+        <v>-1.2219</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1236</v>
+        <v>0.8156</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0762</v>
+        <v>-2.0375</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9135</v>
+        <v>-0.5413</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0414</v>
+        <v>-0.5191</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1279</v>
+        <v>-0.0223</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7761</v>
+        <v>0.5821</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7761</v>
+        <v>1.5523</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7335</v>
+        <v>-1.1008</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.424</v>
+        <v>-0.387</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3095</v>
+        <v>-0.7139</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8358</v>
+        <v>0.2552</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.8358</v>
+        <v>0.2552</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. RIES</t>
+          <t>D. OJEDA DAVILA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7269</v>
+        <v>-2.0892</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9794</v>
+        <v>-0.0762</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2525</v>
+        <v>-2.013</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.7632</v>
+        <v>-0.8661</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2966</v>
+        <v>-0.9177999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0598</v>
+        <v>0.0517</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2219</v>
+        <v>0.0474</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8156</v>
+        <v>0.1236</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.0375</v>
+        <v>-0.0762</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5413</v>
+        <v>-0.9135</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5191</v>
+        <v>-1.0414</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0223</v>
+        <v>0.1279</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5821</v>
+        <v>0.7761</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5523</v>
+        <v>0.7761</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.801</v>
+        <v>-0.1635</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7874</v>
+        <v>-0.1237</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0137</v>
+        <v>-0.0398</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2552</v>
+        <v>-1.8358</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.2552</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4866</v>
+        <v>-2.7619</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5345</v>
+        <v>-1.1341</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9521</v>
+        <v>-1.6278</v>
       </c>
       <c r="G23" t="n">
         <v>-3.4375</v>
@@ -2248,13 +2248,13 @@
         <v>2.7164</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2669</v>
+        <v>-0.5423</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9074</v>
+        <v>-0.507</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3595</v>
+        <v>-0.0353</v>
       </c>
       <c r="V23" t="n">
         <v>0.4418</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ RIVERO</t>
+          <t>O. PEÑA LOPEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.3613</v>
+        <v>-6.6581</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.9267</v>
+        <v>-5.0181</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4347</v>
+        <v>-1.64</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.1656</v>
+        <v>-4.2759</v>
       </c>
       <c r="H24" t="n">
-        <v>-5.5726</v>
+        <v>-1.0504</v>
       </c>
       <c r="I24" t="n">
-        <v>0.407</v>
+        <v>-3.2255</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.8992</v>
+        <v>-1.6601</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.3943</v>
+        <v>0.3419</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5049</v>
+        <v>-2.002</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2664</v>
+        <v>-2.6158</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.1783</v>
+        <v>-1.3924</v>
       </c>
       <c r="O24" t="n">
-        <v>0.912</v>
+        <v>-1.2235</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q24" t="n">
         <v>-2.9105</v>
       </c>
       <c r="R24" t="n">
-        <v>1.9403</v>
+        <v>0.9702</v>
       </c>
       <c r="S24" t="n">
-        <v>2.2804</v>
+        <v>-0.4419</v>
       </c>
       <c r="T24" t="n">
-        <v>1.8831</v>
+        <v>-0.4475</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3973</v>
+        <v>0.0056</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.506</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>O. PEÑA LOPEZ</t>
+          <t>P. RODRIGUEZ RIVERO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.2465</v>
+        <v>-7.1443</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.4185</v>
+        <v>-6.3281</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.828</v>
+        <v>-0.8162</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.2759</v>
+        <v>-5.1656</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.0504</v>
+        <v>-5.5726</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.2255</v>
+        <v>0.407</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.6601</v>
+        <v>-3.8992</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3419</v>
+        <v>-3.3943</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.002</v>
+        <v>-0.5049</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.6158</v>
+        <v>-1.2664</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.3924</v>
+        <v>-2.1783</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.2235</v>
+        <v>0.912</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q25" t="n">
         <v>-2.9105</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9702</v>
+        <v>1.9403</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0303</v>
+        <v>0.4974</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8479</v>
+        <v>0.4817</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1824</v>
+        <v>0.0157</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-15.2491</v>
+        <v>-14.5817</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.729099999999999</v>
+        <v>-4.729000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-10.5199</v>
+        <v>-9.852399999999999</v>
       </c>
       <c r="G26" t="n">
         <v>-18.2726</v>
@@ -2461,7 +2461,7 @@
         <v>10.3396</v>
       </c>
       <c r="L26" t="n">
-        <v>-9.231100000000001</v>
+        <v>-9.2311</v>
       </c>
       <c r="M26" t="n">
         <v>-19.3811</v>
@@ -2482,13 +2482,13 @@
         <v>17.4629</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.0601</v>
+        <v>-3.3929</v>
       </c>
       <c r="T26" t="n">
         <v>-1.621</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.4391</v>
+        <v>-1.772</v>
       </c>
       <c r="V26" t="n">
         <v>3.2029</v>
